--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>718927</v>
+        <v>644261</v>
       </c>
       <c r="B2" t="n">
-        <v>93131</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2604</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623174.7462442745</v>
+        <v>623175</v>
       </c>
       <c r="R2" t="n">
-        <v>6567484.716939207</v>
+        <v>6567485</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2007-03-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-03-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +760,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>bergbrant</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>silikatsten</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5029809</v>
+        <v>718927</v>
       </c>
       <c r="B3" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623174.7462442745</v>
+        <v>623175</v>
       </c>
       <c r="R3" t="n">
-        <v>6567484.716939207</v>
+        <v>6567485</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,21 +850,11 @@
           <t>2007-03-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-03-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +866,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>hasselbrant</t>
+          <t>bergbrant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4805735</v>
+        <v>80526879</v>
       </c>
       <c r="B4" t="n">
-        <v>101679</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +895,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åker, SO om Laketorp vid ån, Srm</t>
+          <t>Strängnäs, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623237.8274234901</v>
+        <v>623266</v>
       </c>
       <c r="R4" t="n">
-        <v>6567564.604979559</v>
+        <v>6567559</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-03-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-03-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,36 +969,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>åravin</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Frank van Spelde</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Frank van Spelde</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>644261</v>
+        <v>88614883</v>
       </c>
       <c r="B5" t="n">
-        <v>95245</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,37 +996,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2604</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åker, Laketorp SO Tjärdal, Srm</t>
+          <t>Strängnäs, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623174.7462442745</v>
+        <v>623052</v>
       </c>
       <c r="R5" t="n">
-        <v>6567484.716939207</v>
+        <v>6567949</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2007-03-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2007-03-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,80 +1070,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>bergbrant</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>silikatsten</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Frank van Spelde</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Frank van Spelde</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88614883</v>
+        <v>2705591</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strängnäs, Srm</t>
+          <t>Åker, SO om Laketorp vid ån, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623052.486318656</v>
+        <v>623193</v>
       </c>
       <c r="R6" t="n">
-        <v>6567949.339037036</v>
+        <v>6567544</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,22 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-03-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-03-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,19 +1167,638 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>åravin</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>78393253</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Laketorpsån , Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>623091</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6567941</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94654624</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strängnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>622960</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568055</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-04-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-04-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Frank van Spelde</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Frank van Spelde</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129092975</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ådals kvarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>622876</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568124</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4805735</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åker, SO om Laketorp vid ån, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623238</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6567565</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2007-03-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2007-03-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>åravin</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5029809</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åker, Laketorp SO Tjärdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>623175</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6567485</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2007-03-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2007-03-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>hasselbrant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>78393107</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Laketorpsån , Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>623026</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6567995</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42335-2025 artfynd.xlsx
+++ b/artfynd/A 42335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/644261</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/718927</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80526879</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88614883</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2705591</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78393253</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94654624</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092975</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4805735</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5029809</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,8 +1854,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78393107</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>